--- a/data/Excel/3.1.xlsx
+++ b/data/Excel/3.1.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="669">
   <si>
     <t>Форма 3.0</t>
   </si>
@@ -234,9 +234,6 @@
   </si>
   <si>
     <t>Суммарная активность, Бк</t>
-  </si>
-  <si>
-    <t>8.1</t>
   </si>
   <si>
     <t>Иридий-192</t>
@@ -2931,7 +2928,7 @@
       <c r="I37" s="11"/>
     </row>
   </sheetData>
-  <sheetProtection formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Ib92QQbilBWjgsgF+0/lp6T/ttqINWw78GFKnKFwVp+SjOJkU7B8mp6qezmekhMZ/mgl3sSSz+0LpBx+XtgWAw==" saltValue="B2+gamwGdD6Sy7r7dS3Psg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1"/>
   <mergeCells count="7">
     <mergeCell ref="A25:A32"/>
     <mergeCell ref="A5:C5"/>
@@ -3190,24 +3187,22 @@
       </c>
     </row>
     <row r="31" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
-        <v>70</v>
-      </c>
+      <c r="A31" s="29"/>
       <c r="B31" s="9"/>
       <c r="C31" s="21"/>
       <c r="D31" s="16"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3216,18 +3211,18 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B40" s="15"/>
     </row>
     <row r="41" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B41" s="27"/>
     </row>
@@ -3239,12 +3234,12 @@
     </row>
     <row r="43" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B43" s="18"/>
     </row>
   </sheetData>
-  <sheetProtection formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="o+HQ9okayVviiwmASRsh9rq9YFqj4ZvbyH/KM4md25/iTnX8ivzBp2Xc1RBRKEZTxXrup8L6h5HVH1lrHDmAdw==" saltValue="Xpoy13jKqtxUV84G2C8tUQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1"/>
   <mergeCells count="6">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="B11:C11"/>
@@ -3307,321 +3302,321 @@
   <sheetData>
     <row r="2" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C2" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="3:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C3" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="K3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2">
         <v>1</v>
       </c>
       <c r="O3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="P3" t="s">
         <v>88</v>
-      </c>
-      <c r="P3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="4" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C4" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="K4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2">
         <v>2</v>
       </c>
       <c r="O4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="P4" t="s">
         <v>94</v>
-      </c>
-      <c r="P4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="5" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C5" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="K5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="O5" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="P5" t="s">
         <v>100</v>
-      </c>
-      <c r="P5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="6" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C6" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="O6" s="3"/>
       <c r="P6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C7" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="K7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="O7" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="P7" t="s">
         <v>111</v>
-      </c>
-      <c r="P7" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="8" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C8" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="K8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="O8" s="3"/>
       <c r="P8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C9" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="K9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="O9" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="P9" t="s">
         <v>122</v>
-      </c>
-      <c r="P9" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="10" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C10" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="K10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="O10" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C11" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="K11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="O11" s="3"/>
       <c r="P11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="3:16" x14ac:dyDescent="0.25">
@@ -3633,57 +3628,57 @@
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="K12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="O12" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="P12" t="s">
         <v>137</v>
-      </c>
-      <c r="P12" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="13" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C13" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E13">
         <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>139</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" t="s">
+        <v>141</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="K13" t="s">
-        <v>142</v>
-      </c>
-      <c r="O13" s="3" t="s">
+      <c r="P13" t="s">
         <v>143</v>
-      </c>
-      <c r="P13" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="14" spans="3:16" x14ac:dyDescent="0.25">
@@ -3691,23 +3686,23 @@
         <v>12</v>
       </c>
       <c r="F14" t="s">
+        <v>144</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="K14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O14" s="3"/>
       <c r="P14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="3:16" x14ac:dyDescent="0.25">
@@ -3715,25 +3710,25 @@
         <v>13</v>
       </c>
       <c r="F15" t="s">
+        <v>148</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="K15" t="s">
+        <v>150</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="K15" t="s">
-        <v>151</v>
-      </c>
-      <c r="O15" s="3" t="s">
+      <c r="P15" t="s">
         <v>152</v>
-      </c>
-      <c r="P15" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="16" spans="3:16" x14ac:dyDescent="0.25">
@@ -3741,25 +3736,25 @@
         <v>14</v>
       </c>
       <c r="F16" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="K16" t="s">
+        <v>155</v>
+      </c>
+      <c r="O16" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="K16" t="s">
-        <v>156</v>
-      </c>
-      <c r="O16" s="3" t="s">
+      <c r="P16" t="s">
         <v>157</v>
-      </c>
-      <c r="P16" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="17" spans="5:16" x14ac:dyDescent="0.25">
@@ -3767,25 +3762,25 @@
         <v>15</v>
       </c>
       <c r="F17" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="K17" t="s">
+        <v>160</v>
+      </c>
+      <c r="O17" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K17" t="s">
-        <v>161</v>
-      </c>
-      <c r="O17" s="3" t="s">
+      <c r="P17" t="s">
         <v>162</v>
-      </c>
-      <c r="P17" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="18" spans="5:16" x14ac:dyDescent="0.25">
@@ -3793,25 +3788,25 @@
         <v>16</v>
       </c>
       <c r="F18" t="s">
+        <v>163</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" t="s">
+        <v>165</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="K18" t="s">
-        <v>166</v>
-      </c>
-      <c r="O18" s="3" t="s">
+      <c r="P18" t="s">
         <v>167</v>
-      </c>
-      <c r="P18" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="19" spans="5:16" x14ac:dyDescent="0.25">
@@ -3819,25 +3814,25 @@
         <v>17</v>
       </c>
       <c r="F19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" t="s">
+        <v>170</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="K19" t="s">
-        <v>171</v>
-      </c>
-      <c r="O19" s="3" t="s">
+      <c r="P19" t="s">
         <v>172</v>
-      </c>
-      <c r="P19" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="20" spans="5:16" x14ac:dyDescent="0.25">
@@ -3845,23 +3840,23 @@
         <v>18</v>
       </c>
       <c r="F20" t="s">
+        <v>173</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="K20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="5:16" x14ac:dyDescent="0.25">
@@ -3869,25 +3864,25 @@
         <v>19</v>
       </c>
       <c r="F21" t="s">
+        <v>177</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" t="s">
+        <v>179</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="K21" t="s">
-        <v>180</v>
-      </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" t="s">
         <v>181</v>
-      </c>
-      <c r="P21" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="22" spans="5:16" x14ac:dyDescent="0.25">
@@ -3895,23 +3890,23 @@
         <v>20</v>
       </c>
       <c r="F22" t="s">
+        <v>182</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="K22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="5:16" x14ac:dyDescent="0.25">
@@ -3919,25 +3914,25 @@
         <v>21</v>
       </c>
       <c r="F23" t="s">
+        <v>186</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="I23" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="K23" t="s">
+        <v>189</v>
+      </c>
+      <c r="O23" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="K23" t="s">
-        <v>190</v>
-      </c>
-      <c r="O23" s="3" t="s">
+      <c r="P23" t="s">
         <v>191</v>
-      </c>
-      <c r="P23" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="24" spans="5:16" x14ac:dyDescent="0.25">
@@ -3945,25 +3940,25 @@
         <v>22</v>
       </c>
       <c r="F24" t="s">
+        <v>192</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="K24" t="s">
+        <v>194</v>
+      </c>
+      <c r="O24" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K24" t="s">
-        <v>195</v>
-      </c>
-      <c r="O24" s="3" t="s">
+      <c r="P24" t="s">
         <v>196</v>
-      </c>
-      <c r="P24" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="25" spans="5:16" x14ac:dyDescent="0.25">
@@ -3971,23 +3966,23 @@
         <v>23</v>
       </c>
       <c r="F25" t="s">
+        <v>197</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="K25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O25" s="3"/>
       <c r="P25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="5:16" x14ac:dyDescent="0.25">
@@ -3995,25 +3990,25 @@
         <v>24</v>
       </c>
       <c r="F26" t="s">
+        <v>201</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="K26" t="s">
+        <v>203</v>
+      </c>
+      <c r="O26" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="K26" t="s">
-        <v>204</v>
-      </c>
-      <c r="O26" s="3" t="s">
+      <c r="P26" t="s">
         <v>205</v>
-      </c>
-      <c r="P26" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="27" spans="5:16" x14ac:dyDescent="0.25">
@@ -4021,23 +4016,23 @@
         <v>25</v>
       </c>
       <c r="F27" t="s">
+        <v>206</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="K27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="5:16" x14ac:dyDescent="0.25">
@@ -4045,25 +4040,25 @@
         <v>26</v>
       </c>
       <c r="F28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="K28" t="s">
+        <v>212</v>
+      </c>
+      <c r="O28" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K28" t="s">
-        <v>213</v>
-      </c>
-      <c r="O28" s="3" t="s">
+      <c r="P28" t="s">
         <v>214</v>
-      </c>
-      <c r="P28" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="29" spans="5:16" x14ac:dyDescent="0.25">
@@ -4071,19 +4066,19 @@
         <v>27</v>
       </c>
       <c r="F29" t="s">
+        <v>215</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="K29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="2"/>
@@ -4093,19 +4088,19 @@
         <v>28</v>
       </c>
       <c r="F30" t="s">
+        <v>218</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="I30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="K30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O30" s="3"/>
     </row>
@@ -4114,19 +4109,19 @@
         <v>29</v>
       </c>
       <c r="F31" t="s">
+        <v>221</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="I31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>224</v>
-      </c>
       <c r="K31" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O31" s="3"/>
     </row>
@@ -4135,22 +4130,22 @@
         <v>30</v>
       </c>
       <c r="F32" t="s">
+        <v>224</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="K32" t="s">
+        <v>226</v>
+      </c>
+      <c r="O32" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="K32" t="s">
-        <v>227</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="33" spans="5:15" x14ac:dyDescent="0.25">
@@ -4158,19 +4153,19 @@
         <v>31</v>
       </c>
       <c r="F33" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I33" s="3">
         <v>100</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K33" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O33" s="3"/>
     </row>
@@ -4179,22 +4174,22 @@
         <v>32</v>
       </c>
       <c r="F34" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I34" s="3">
         <v>104</v>
       </c>
       <c r="J34" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="K34" t="s">
+        <v>231</v>
+      </c>
+      <c r="O34" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="K34" t="s">
-        <v>232</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="35" spans="5:15" x14ac:dyDescent="0.25">
@@ -4202,22 +4197,22 @@
         <v>33</v>
       </c>
       <c r="F35" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I35" s="3">
         <v>108</v>
       </c>
       <c r="J35" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="K35" t="s">
+        <v>234</v>
+      </c>
+      <c r="O35" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="K35" t="s">
-        <v>235</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="36" spans="5:15" x14ac:dyDescent="0.25">
@@ -4225,22 +4220,22 @@
         <v>34</v>
       </c>
       <c r="F36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I36" s="3">
         <v>112</v>
       </c>
       <c r="J36" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K36" t="s">
+        <v>237</v>
+      </c>
+      <c r="O36" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="K36" t="s">
-        <v>238</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="37" spans="5:15" x14ac:dyDescent="0.25">
@@ -4248,22 +4243,22 @@
         <v>35</v>
       </c>
       <c r="F37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I37" s="3">
         <v>116</v>
       </c>
       <c r="J37" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="K37" t="s">
+        <v>240</v>
+      </c>
+      <c r="O37" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="K37" t="s">
-        <v>241</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="38" spans="5:15" x14ac:dyDescent="0.25">
@@ -4271,22 +4266,22 @@
         <v>36</v>
       </c>
       <c r="F38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I38" s="3">
         <v>120</v>
       </c>
       <c r="J38" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="K38" t="s">
+        <v>243</v>
+      </c>
+      <c r="O38" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="K38" t="s">
-        <v>244</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="39" spans="5:15" x14ac:dyDescent="0.25">
@@ -4294,22 +4289,22 @@
         <v>37</v>
       </c>
       <c r="F39" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I39" s="3">
         <v>124</v>
       </c>
       <c r="J39" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="K39" t="s">
+        <v>246</v>
+      </c>
+      <c r="O39" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="K39" t="s">
-        <v>247</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="40" spans="5:15" x14ac:dyDescent="0.25">
@@ -4317,19 +4312,19 @@
         <v>38</v>
       </c>
       <c r="F40" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I40" s="3">
         <v>132</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K40" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O40" s="3"/>
     </row>
@@ -4338,22 +4333,22 @@
         <v>39</v>
       </c>
       <c r="F41" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I41" s="3">
         <v>136</v>
       </c>
       <c r="J41" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="K41" t="s">
+        <v>251</v>
+      </c>
+      <c r="O41" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="K41" t="s">
-        <v>252</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="42" spans="5:15" x14ac:dyDescent="0.25">
@@ -4361,19 +4356,19 @@
         <v>40</v>
       </c>
       <c r="F42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I42" s="3">
         <v>140</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K42" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O42" s="3"/>
     </row>
@@ -4382,19 +4377,19 @@
         <v>41</v>
       </c>
       <c r="F43" t="s">
+        <v>255</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="I43" s="3">
         <v>144</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K43" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O43" s="3"/>
     </row>
@@ -4403,22 +4398,22 @@
         <v>42</v>
       </c>
       <c r="F44" t="s">
+        <v>258</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="I44" s="3">
         <v>148</v>
       </c>
       <c r="J44" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="K44" t="s">
+        <v>260</v>
+      </c>
+      <c r="O44" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="K44" t="s">
-        <v>261</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="45" spans="5:15" x14ac:dyDescent="0.25">
@@ -4426,22 +4421,22 @@
         <v>43</v>
       </c>
       <c r="F45" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I45" s="3">
         <v>152</v>
       </c>
       <c r="J45" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="K45" t="s">
+        <v>263</v>
+      </c>
+      <c r="O45" s="3" t="s">
         <v>264</v>
-      </c>
-      <c r="K45" t="s">
-        <v>264</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="46" spans="5:15" x14ac:dyDescent="0.25">
@@ -4449,22 +4444,22 @@
         <v>44</v>
       </c>
       <c r="F46" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I46" s="3">
         <v>156</v>
       </c>
       <c r="J46" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K46" t="s">
+        <v>266</v>
+      </c>
+      <c r="O46" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="K46" t="s">
-        <v>267</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="47" spans="5:15" x14ac:dyDescent="0.25">
@@ -4472,22 +4467,22 @@
         <v>45</v>
       </c>
       <c r="F47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I47" s="3">
         <v>158</v>
       </c>
       <c r="J47" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="K47" t="s">
+        <v>269</v>
+      </c>
+      <c r="O47" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="K47" t="s">
-        <v>270</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="48" spans="5:15" x14ac:dyDescent="0.25">
@@ -4495,19 +4490,19 @@
         <v>46</v>
       </c>
       <c r="F48" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I48" s="3">
         <v>162</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K48" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O48" s="3"/>
     </row>
@@ -4516,19 +4511,19 @@
         <v>47</v>
       </c>
       <c r="F49" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I49" s="3">
         <v>166</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K49" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O49" s="3"/>
     </row>
@@ -4537,19 +4532,19 @@
         <v>48</v>
       </c>
       <c r="F50" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I50" s="3">
         <v>170</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O50" s="3"/>
     </row>
@@ -4558,22 +4553,22 @@
         <v>49</v>
       </c>
       <c r="F51" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I51" s="3">
         <v>174</v>
       </c>
       <c r="J51" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="K51" t="s">
+        <v>278</v>
+      </c>
+      <c r="O51" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="K51" t="s">
-        <v>279</v>
-      </c>
-      <c r="O51" s="3" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="52" spans="5:15" x14ac:dyDescent="0.25">
@@ -4581,22 +4576,22 @@
         <v>50</v>
       </c>
       <c r="F52" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I52" s="3">
         <v>175</v>
       </c>
       <c r="J52" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="K52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O52" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="K52" t="s">
-        <v>282</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="53" spans="5:15" x14ac:dyDescent="0.25">
@@ -4604,19 +4599,19 @@
         <v>51</v>
       </c>
       <c r="F53" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I53" s="3">
         <v>178</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K53" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O53" s="3"/>
     </row>
@@ -4625,22 +4620,22 @@
         <v>52</v>
       </c>
       <c r="F54" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I54" s="3">
         <v>180</v>
       </c>
       <c r="J54" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K54" t="s">
+        <v>286</v>
+      </c>
+      <c r="O54" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="K54" t="s">
-        <v>287</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="55" spans="5:15" x14ac:dyDescent="0.25">
@@ -4648,22 +4643,22 @@
         <v>53</v>
       </c>
       <c r="F55" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I55" s="3">
         <v>184</v>
       </c>
       <c r="J55" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="K55" t="s">
+        <v>289</v>
+      </c>
+      <c r="O55" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="K55" t="s">
-        <v>290</v>
-      </c>
-      <c r="O55" s="3" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="56" spans="5:15" x14ac:dyDescent="0.25">
@@ -4671,19 +4666,19 @@
         <v>54</v>
       </c>
       <c r="F56" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I56" s="3">
         <v>188</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K56" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O56" s="3"/>
     </row>
@@ -4692,22 +4687,22 @@
         <v>55</v>
       </c>
       <c r="F57" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I57" s="3">
         <v>191</v>
       </c>
       <c r="J57" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="K57" t="s">
+        <v>294</v>
+      </c>
+      <c r="O57" s="3" t="s">
         <v>295</v>
-      </c>
-      <c r="K57" t="s">
-        <v>295</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="58" spans="5:15" x14ac:dyDescent="0.25">
@@ -4715,22 +4710,22 @@
         <v>56</v>
       </c>
       <c r="F58" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I58" s="3">
         <v>192</v>
       </c>
       <c r="J58" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K58" t="s">
+        <v>297</v>
+      </c>
+      <c r="O58" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="K58" t="s">
-        <v>298</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="59" spans="5:15" x14ac:dyDescent="0.25">
@@ -4738,22 +4733,22 @@
         <v>57</v>
       </c>
       <c r="F59" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I59" s="3">
         <v>196</v>
       </c>
       <c r="J59" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="K59" t="s">
+        <v>300</v>
+      </c>
+      <c r="O59" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="K59" t="s">
-        <v>301</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="60" spans="5:15" x14ac:dyDescent="0.25">
@@ -4761,22 +4756,22 @@
         <v>58</v>
       </c>
       <c r="F60" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I60" s="3">
         <v>203</v>
       </c>
       <c r="J60" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="K60" t="s">
+        <v>303</v>
+      </c>
+      <c r="O60" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="K60" t="s">
-        <v>304</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="61" spans="5:15" x14ac:dyDescent="0.25">
@@ -4784,22 +4779,22 @@
         <v>59</v>
       </c>
       <c r="F61" t="s">
+        <v>305</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="I61" s="3">
         <v>204</v>
       </c>
       <c r="J61" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="K61" t="s">
+        <v>307</v>
+      </c>
+      <c r="O61" s="3" t="s">
         <v>308</v>
-      </c>
-      <c r="K61" t="s">
-        <v>308</v>
-      </c>
-      <c r="O61" s="3" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="62" spans="5:15" x14ac:dyDescent="0.25">
@@ -4807,22 +4802,22 @@
         <v>60</v>
       </c>
       <c r="F62" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I62" s="3">
         <v>208</v>
       </c>
       <c r="J62" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="K62" t="s">
+        <v>310</v>
+      </c>
+      <c r="O62" s="3" t="s">
         <v>311</v>
-      </c>
-      <c r="K62" t="s">
-        <v>311</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="63" spans="5:15" x14ac:dyDescent="0.25">
@@ -4830,22 +4825,22 @@
         <v>61</v>
       </c>
       <c r="F63" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I63" s="3">
         <v>212</v>
       </c>
       <c r="J63" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="K63" t="s">
+        <v>313</v>
+      </c>
+      <c r="O63" s="3" t="s">
         <v>314</v>
-      </c>
-      <c r="K63" t="s">
-        <v>314</v>
-      </c>
-      <c r="O63" s="3" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="64" spans="5:15" x14ac:dyDescent="0.25">
@@ -4853,22 +4848,22 @@
         <v>62</v>
       </c>
       <c r="F64" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I64" s="3">
         <v>214</v>
       </c>
       <c r="J64" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="K64" t="s">
+        <v>316</v>
+      </c>
+      <c r="O64" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="K64" t="s">
-        <v>317</v>
-      </c>
-      <c r="O64" s="3" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="65" spans="5:15" x14ac:dyDescent="0.25">
@@ -4876,19 +4871,19 @@
         <v>63</v>
       </c>
       <c r="F65" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I65" s="3">
         <v>218</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K65" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O65" s="3"/>
     </row>
@@ -4897,22 +4892,22 @@
         <v>64</v>
       </c>
       <c r="F66" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I66" s="3">
         <v>222</v>
       </c>
       <c r="J66" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="K66" t="s">
+        <v>321</v>
+      </c>
+      <c r="O66" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="K66" t="s">
-        <v>322</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="67" spans="5:15" x14ac:dyDescent="0.25">
@@ -4920,22 +4915,22 @@
         <v>65</v>
       </c>
       <c r="F67" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I67" s="3">
         <v>226</v>
       </c>
       <c r="J67" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="K67" t="s">
+        <v>324</v>
+      </c>
+      <c r="O67" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="K67" t="s">
-        <v>325</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="68" spans="5:15" x14ac:dyDescent="0.25">
@@ -4952,13 +4947,13 @@
         <v>231</v>
       </c>
       <c r="J68" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="K68" t="s">
+        <v>326</v>
+      </c>
+      <c r="O68" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="K68" t="s">
-        <v>327</v>
-      </c>
-      <c r="O68" s="3" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="69" spans="5:15" x14ac:dyDescent="0.25">
@@ -4966,22 +4961,22 @@
         <v>67</v>
       </c>
       <c r="F69" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I69" s="3">
         <v>232</v>
       </c>
       <c r="J69" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K69" t="s">
+        <v>329</v>
+      </c>
+      <c r="O69" s="3" t="s">
         <v>330</v>
-      </c>
-      <c r="K69" t="s">
-        <v>330</v>
-      </c>
-      <c r="O69" s="3" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="70" spans="5:15" x14ac:dyDescent="0.25">
@@ -4989,22 +4984,22 @@
         <v>68</v>
       </c>
       <c r="F70" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I70" s="3">
         <v>233</v>
       </c>
       <c r="J70" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K70" t="s">
+        <v>332</v>
+      </c>
+      <c r="O70" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="K70" t="s">
-        <v>333</v>
-      </c>
-      <c r="O70" s="3" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="71" spans="5:15" x14ac:dyDescent="0.25">
@@ -5012,22 +5007,22 @@
         <v>69</v>
       </c>
       <c r="F71" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I71" s="3">
         <v>234</v>
       </c>
       <c r="J71" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="K71" t="s">
+        <v>335</v>
+      </c>
+      <c r="O71" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="K71" t="s">
-        <v>336</v>
-      </c>
-      <c r="O71" s="3" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="72" spans="5:15" x14ac:dyDescent="0.25">
@@ -5035,19 +5030,19 @@
         <v>70</v>
       </c>
       <c r="F72" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I72" s="3">
         <v>238</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K72" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O72" s="3"/>
     </row>
@@ -5056,19 +5051,19 @@
         <v>71</v>
       </c>
       <c r="F73" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I73" s="3">
         <v>239</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K73" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O73" s="3"/>
     </row>
@@ -5077,19 +5072,19 @@
         <v>72</v>
       </c>
       <c r="F74" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I74" s="3">
         <v>242</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K74" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O74" s="3"/>
     </row>
@@ -5098,22 +5093,22 @@
         <v>73</v>
       </c>
       <c r="F75" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I75" s="3">
         <v>246</v>
       </c>
       <c r="J75" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="K75" t="s">
+        <v>344</v>
+      </c>
+      <c r="O75" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="K75" t="s">
-        <v>345</v>
-      </c>
-      <c r="O75" s="3" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="76" spans="5:15" x14ac:dyDescent="0.25">
@@ -5121,22 +5116,22 @@
         <v>74</v>
       </c>
       <c r="F76" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I76" s="3">
         <v>248</v>
       </c>
       <c r="J76" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="K76" t="s">
+        <v>347</v>
+      </c>
+      <c r="O76" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="K76" t="s">
-        <v>348</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="77" spans="5:15" x14ac:dyDescent="0.25">
@@ -5144,19 +5139,19 @@
         <v>75</v>
       </c>
       <c r="F77" t="s">
+        <v>349</v>
+      </c>
+      <c r="G77" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="I77" s="3">
         <v>250</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K77" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O77" s="3"/>
     </row>
@@ -5165,22 +5160,22 @@
         <v>76</v>
       </c>
       <c r="F78" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I78" s="3">
         <v>254</v>
       </c>
       <c r="J78" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="K78" t="s">
+        <v>353</v>
+      </c>
+      <c r="O78" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="K78" t="s">
-        <v>354</v>
-      </c>
-      <c r="O78" s="3" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="79" spans="5:15" x14ac:dyDescent="0.25">
@@ -5188,19 +5183,19 @@
         <v>77</v>
       </c>
       <c r="F79" t="s">
+        <v>355</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="I79" s="3">
         <v>258</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K79" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O79" s="3"/>
     </row>
@@ -5209,19 +5204,19 @@
         <v>78</v>
       </c>
       <c r="F80" t="s">
+        <v>358</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="I80" s="3">
         <v>260</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K80" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O80" s="3"/>
     </row>
@@ -5230,19 +5225,19 @@
         <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I81" s="3">
         <v>262</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K81" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O81" s="3"/>
     </row>
@@ -5251,22 +5246,22 @@
         <v>83</v>
       </c>
       <c r="F82" t="s">
+        <v>363</v>
+      </c>
+      <c r="G82" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="I82" s="3">
         <v>266</v>
       </c>
       <c r="J82" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="K82" t="s">
+        <v>365</v>
+      </c>
+      <c r="O82" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="K82" t="s">
-        <v>366</v>
-      </c>
-      <c r="O82" s="3" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="83" spans="5:15" x14ac:dyDescent="0.25">
@@ -5274,22 +5269,22 @@
         <v>86</v>
       </c>
       <c r="F83" t="s">
+        <v>367</v>
+      </c>
+      <c r="G83" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="I83" s="3">
         <v>268</v>
       </c>
       <c r="J83" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="K83" t="s">
+        <v>369</v>
+      </c>
+      <c r="O83" s="3" t="s">
         <v>370</v>
-      </c>
-      <c r="K83" t="s">
-        <v>370</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="84" spans="5:15" x14ac:dyDescent="0.25">
@@ -5297,19 +5292,19 @@
         <v>87</v>
       </c>
       <c r="F84" t="s">
+        <v>371</v>
+      </c>
+      <c r="G84" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="I84" s="3">
         <v>270</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K84" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="O84" s="3"/>
     </row>
@@ -5318,22 +5313,22 @@
         <v>89</v>
       </c>
       <c r="F85" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I85" s="3">
         <v>275</v>
       </c>
       <c r="J85" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="K85" t="s">
+        <v>375</v>
+      </c>
+      <c r="O85" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="K85" t="s">
-        <v>376</v>
-      </c>
-      <c r="O85" s="3" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="86" spans="5:15" x14ac:dyDescent="0.25">
@@ -5341,22 +5336,22 @@
         <v>91</v>
       </c>
       <c r="F86" t="s">
+        <v>377</v>
+      </c>
+      <c r="G86" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="I86" s="3">
         <v>276</v>
       </c>
       <c r="J86" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="K86" t="s">
+        <v>379</v>
+      </c>
+      <c r="O86" s="3" t="s">
         <v>380</v>
-      </c>
-      <c r="K86" t="s">
-        <v>380</v>
-      </c>
-      <c r="O86" s="3" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="87" spans="5:15" x14ac:dyDescent="0.25">
@@ -5364,22 +5359,22 @@
         <v>92</v>
       </c>
       <c r="F87" t="s">
+        <v>381</v>
+      </c>
+      <c r="G87" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="I87" s="3">
         <v>288</v>
       </c>
       <c r="J87" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="K87" t="s">
+        <v>383</v>
+      </c>
+      <c r="O87" s="3" t="s">
         <v>384</v>
-      </c>
-      <c r="K87" t="s">
-        <v>384</v>
-      </c>
-      <c r="O87" s="3" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="88" spans="5:15" x14ac:dyDescent="0.25">
@@ -5387,22 +5382,22 @@
         <v>99</v>
       </c>
       <c r="F88" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I88" s="3">
         <v>292</v>
       </c>
       <c r="J88" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="K88" t="s">
+        <v>386</v>
+      </c>
+      <c r="O88" s="3" t="s">
         <v>387</v>
-      </c>
-      <c r="K88" t="s">
-        <v>387</v>
-      </c>
-      <c r="O88" s="3" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="89" spans="5:15" x14ac:dyDescent="0.25">
@@ -5410,10 +5405,10 @@
         <v>296</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K89" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="O89" s="3"/>
     </row>
@@ -5422,13 +5417,13 @@
         <v>300</v>
       </c>
       <c r="J90" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="K90" t="s">
+        <v>389</v>
+      </c>
+      <c r="O90" s="3" t="s">
         <v>390</v>
-      </c>
-      <c r="K90" t="s">
-        <v>390</v>
-      </c>
-      <c r="O90" s="3" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="91" spans="5:15" x14ac:dyDescent="0.25">
@@ -5436,13 +5431,13 @@
         <v>304</v>
       </c>
       <c r="J91" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="K91" t="s">
+        <v>391</v>
+      </c>
+      <c r="O91" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="K91" t="s">
-        <v>392</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="92" spans="5:15" x14ac:dyDescent="0.25">
@@ -5450,10 +5445,10 @@
         <v>308</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K92" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O92" s="3"/>
     </row>
@@ -5462,10 +5457,10 @@
         <v>312</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K93" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O93" s="3"/>
     </row>
@@ -5474,10 +5469,10 @@
         <v>316</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K94" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O94" s="3"/>
     </row>
@@ -5486,10 +5481,10 @@
         <v>320</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K95" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O95" s="3"/>
     </row>
@@ -5498,13 +5493,13 @@
         <v>324</v>
       </c>
       <c r="J96" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="K96" t="s">
+        <v>397</v>
+      </c>
+      <c r="O96" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="K96" t="s">
-        <v>398</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="97" spans="9:15" x14ac:dyDescent="0.25">
@@ -5512,13 +5507,13 @@
         <v>328</v>
       </c>
       <c r="J97" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="K97" t="s">
+        <v>399</v>
+      </c>
+      <c r="O97" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="K97" t="s">
-        <v>400</v>
-      </c>
-      <c r="O97" s="3" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="98" spans="9:15" x14ac:dyDescent="0.25">
@@ -5526,13 +5521,13 @@
         <v>332</v>
       </c>
       <c r="J98" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="K98" t="s">
+        <v>401</v>
+      </c>
+      <c r="O98" s="3" t="s">
         <v>402</v>
-      </c>
-      <c r="K98" t="s">
-        <v>402</v>
-      </c>
-      <c r="O98" s="3" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="99" spans="9:15" x14ac:dyDescent="0.25">
@@ -5540,13 +5535,13 @@
         <v>334</v>
       </c>
       <c r="J99" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="K99" t="s">
+        <v>403</v>
+      </c>
+      <c r="O99" s="3" t="s">
         <v>404</v>
-      </c>
-      <c r="K99" t="s">
-        <v>404</v>
-      </c>
-      <c r="O99" s="3" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="100" spans="9:15" x14ac:dyDescent="0.25">
@@ -5554,10 +5549,10 @@
         <v>336</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K100" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="O100" s="3"/>
     </row>
@@ -5566,10 +5561,10 @@
         <v>340</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K101" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="O101" s="3"/>
     </row>
@@ -5578,13 +5573,13 @@
         <v>344</v>
       </c>
       <c r="J102" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="K102" t="s">
+        <v>407</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="K102" t="s">
-        <v>408</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="103" spans="9:15" x14ac:dyDescent="0.25">
@@ -5592,13 +5587,13 @@
         <v>348</v>
       </c>
       <c r="J103" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="K103" t="s">
+        <v>409</v>
+      </c>
+      <c r="O103" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="K103" t="s">
-        <v>410</v>
-      </c>
-      <c r="O103" s="3" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="104" spans="9:15" x14ac:dyDescent="0.25">
@@ -5606,13 +5601,13 @@
         <v>352</v>
       </c>
       <c r="J104" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="K104" t="s">
+        <v>411</v>
+      </c>
+      <c r="O104" s="3" t="s">
         <v>412</v>
-      </c>
-      <c r="K104" t="s">
-        <v>412</v>
-      </c>
-      <c r="O104" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="105" spans="9:15" x14ac:dyDescent="0.25">
@@ -5620,13 +5615,13 @@
         <v>356</v>
       </c>
       <c r="J105" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="K105" t="s">
+        <v>413</v>
+      </c>
+      <c r="O105" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="K105" t="s">
-        <v>414</v>
-      </c>
-      <c r="O105" s="3" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="106" spans="9:15" x14ac:dyDescent="0.25">
@@ -5634,13 +5629,13 @@
         <v>360</v>
       </c>
       <c r="J106" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="K106" t="s">
+        <v>415</v>
+      </c>
+      <c r="O106" s="3" t="s">
         <v>416</v>
-      </c>
-      <c r="K106" t="s">
-        <v>416</v>
-      </c>
-      <c r="O106" s="3" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="107" spans="9:15" x14ac:dyDescent="0.25">
@@ -5648,13 +5643,13 @@
         <v>364</v>
       </c>
       <c r="J107" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="K107" t="s">
+        <v>417</v>
+      </c>
+      <c r="O107" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="K107" t="s">
-        <v>418</v>
-      </c>
-      <c r="O107" s="3" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="108" spans="9:15" x14ac:dyDescent="0.25">
@@ -5662,13 +5657,13 @@
         <v>368</v>
       </c>
       <c r="J108" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="K108" t="s">
+        <v>419</v>
+      </c>
+      <c r="O108" s="3" t="s">
         <v>420</v>
-      </c>
-      <c r="K108" t="s">
-        <v>420</v>
-      </c>
-      <c r="O108" s="3" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="109" spans="9:15" x14ac:dyDescent="0.25">
@@ -5676,13 +5671,13 @@
         <v>372</v>
       </c>
       <c r="J109" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="K109" t="s">
+        <v>421</v>
+      </c>
+      <c r="O109" s="3" t="s">
         <v>422</v>
-      </c>
-      <c r="K109" t="s">
-        <v>422</v>
-      </c>
-      <c r="O109" s="3" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="110" spans="9:15" x14ac:dyDescent="0.25">
@@ -5690,10 +5685,10 @@
         <v>376</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K110" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O110" s="3"/>
     </row>
@@ -5702,13 +5697,13 @@
         <v>380</v>
       </c>
       <c r="J111" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="K111" t="s">
+        <v>424</v>
+      </c>
+      <c r="O111" s="3" t="s">
         <v>425</v>
-      </c>
-      <c r="K111" t="s">
-        <v>425</v>
-      </c>
-      <c r="O111" s="3" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="112" spans="9:15" x14ac:dyDescent="0.25">
@@ -5716,13 +5711,13 @@
         <v>384</v>
       </c>
       <c r="J112" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="K112" t="s">
+        <v>426</v>
+      </c>
+      <c r="O112" s="3" t="s">
         <v>427</v>
-      </c>
-      <c r="K112" t="s">
-        <v>427</v>
-      </c>
-      <c r="O112" s="3" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="113" spans="9:15" x14ac:dyDescent="0.25">
@@ -5730,13 +5725,13 @@
         <v>388</v>
       </c>
       <c r="J113" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="K113" t="s">
+        <v>428</v>
+      </c>
+      <c r="O113" s="3" t="s">
         <v>429</v>
-      </c>
-      <c r="K113" t="s">
-        <v>429</v>
-      </c>
-      <c r="O113" s="3" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="114" spans="9:15" x14ac:dyDescent="0.25">
@@ -5744,10 +5739,10 @@
         <v>392</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K114" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O114" s="3"/>
     </row>
@@ -5756,10 +5751,10 @@
         <v>398</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K115" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="O115" s="3"/>
     </row>
@@ -5768,13 +5763,13 @@
         <v>400</v>
       </c>
       <c r="J116" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="K116" t="s">
+        <v>432</v>
+      </c>
+      <c r="O116" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="K116" t="s">
-        <v>433</v>
-      </c>
-      <c r="O116" s="3" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="117" spans="9:15" x14ac:dyDescent="0.25">
@@ -5782,13 +5777,13 @@
         <v>404</v>
       </c>
       <c r="J117" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="K117" t="s">
+        <v>434</v>
+      </c>
+      <c r="O117" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="K117" t="s">
-        <v>435</v>
-      </c>
-      <c r="O117" s="3" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="118" spans="9:15" x14ac:dyDescent="0.25">
@@ -5796,13 +5791,13 @@
         <v>408</v>
       </c>
       <c r="J118" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="K118" t="s">
+        <v>436</v>
+      </c>
+      <c r="O118" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="K118" t="s">
-        <v>437</v>
-      </c>
-      <c r="O118" s="3" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="119" spans="9:15" x14ac:dyDescent="0.25">
@@ -5810,13 +5805,13 @@
         <v>410</v>
       </c>
       <c r="J119" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="K119" t="s">
+        <v>438</v>
+      </c>
+      <c r="O119" s="3" t="s">
         <v>439</v>
-      </c>
-      <c r="K119" t="s">
-        <v>439</v>
-      </c>
-      <c r="O119" s="3" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="120" spans="9:15" x14ac:dyDescent="0.25">
@@ -5824,13 +5819,13 @@
         <v>414</v>
       </c>
       <c r="J120" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="K120" t="s">
+        <v>440</v>
+      </c>
+      <c r="O120" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="K120" t="s">
-        <v>441</v>
-      </c>
-      <c r="O120" s="3" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="121" spans="9:15" x14ac:dyDescent="0.25">
@@ -5838,13 +5833,13 @@
         <v>417</v>
       </c>
       <c r="J121" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="K121" t="s">
+        <v>442</v>
+      </c>
+      <c r="O121" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="K121" t="s">
-        <v>443</v>
-      </c>
-      <c r="O121" s="3" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="122" spans="9:15" x14ac:dyDescent="0.25">
@@ -5852,13 +5847,13 @@
         <v>418</v>
       </c>
       <c r="J122" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="K122" t="s">
+        <v>444</v>
+      </c>
+      <c r="O122" s="3" t="s">
         <v>445</v>
-      </c>
-      <c r="K122" t="s">
-        <v>445</v>
-      </c>
-      <c r="O122" s="3" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="123" spans="9:15" x14ac:dyDescent="0.25">
@@ -5866,10 +5861,10 @@
         <v>422</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="K123" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="O123" s="3"/>
     </row>
@@ -5878,13 +5873,13 @@
         <v>426</v>
       </c>
       <c r="J124" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="K124" t="s">
+        <v>447</v>
+      </c>
+      <c r="O124" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="K124" t="s">
-        <v>448</v>
-      </c>
-      <c r="O124" s="3" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="125" spans="9:15" x14ac:dyDescent="0.25">
@@ -5892,13 +5887,13 @@
         <v>428</v>
       </c>
       <c r="J125" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="K125" t="s">
+        <v>449</v>
+      </c>
+      <c r="O125" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="K125" t="s">
-        <v>450</v>
-      </c>
-      <c r="O125" s="3" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="126" spans="9:15" x14ac:dyDescent="0.25">
@@ -5906,13 +5901,13 @@
         <v>430</v>
       </c>
       <c r="J126" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="K126" t="s">
+        <v>451</v>
+      </c>
+      <c r="O126" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="K126" t="s">
-        <v>452</v>
-      </c>
-      <c r="O126" s="3" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="127" spans="9:15" x14ac:dyDescent="0.25">
@@ -5920,13 +5915,13 @@
         <v>434</v>
       </c>
       <c r="J127" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="K127" t="s">
+        <v>453</v>
+      </c>
+      <c r="O127" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="K127" t="s">
-        <v>454</v>
-      </c>
-      <c r="O127" s="3" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="128" spans="9:15" x14ac:dyDescent="0.25">
@@ -5934,13 +5929,13 @@
         <v>438</v>
       </c>
       <c r="J128" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="K128" t="s">
+        <v>455</v>
+      </c>
+      <c r="O128" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="K128" t="s">
-        <v>456</v>
-      </c>
-      <c r="O128" s="3" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="129" spans="9:15" x14ac:dyDescent="0.25">
@@ -5948,13 +5943,13 @@
         <v>440</v>
       </c>
       <c r="J129" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="K129" t="s">
+        <v>457</v>
+      </c>
+      <c r="O129" s="3" t="s">
         <v>458</v>
-      </c>
-      <c r="K129" t="s">
-        <v>458</v>
-      </c>
-      <c r="O129" s="3" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="130" spans="9:15" x14ac:dyDescent="0.25">
@@ -5962,13 +5957,13 @@
         <v>442</v>
       </c>
       <c r="J130" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K130" t="s">
+        <v>459</v>
+      </c>
+      <c r="O130" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="K130" t="s">
-        <v>460</v>
-      </c>
-      <c r="O130" s="3" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="131" spans="9:15" x14ac:dyDescent="0.25">
@@ -5976,13 +5971,13 @@
         <v>446</v>
       </c>
       <c r="J131" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="K131" t="s">
+        <v>461</v>
+      </c>
+      <c r="O131" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="K131" t="s">
-        <v>462</v>
-      </c>
-      <c r="O131" s="3" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="132" spans="9:15" x14ac:dyDescent="0.25">
@@ -5990,13 +5985,13 @@
         <v>450</v>
       </c>
       <c r="J132" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="K132" t="s">
+        <v>463</v>
+      </c>
+      <c r="O132" s="3" t="s">
         <v>464</v>
-      </c>
-      <c r="K132" t="s">
-        <v>464</v>
-      </c>
-      <c r="O132" s="3" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="133" spans="9:15" x14ac:dyDescent="0.25">
@@ -6004,13 +5999,13 @@
         <v>454</v>
       </c>
       <c r="J133" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="K133" t="s">
+        <v>465</v>
+      </c>
+      <c r="O133" s="3" t="s">
         <v>466</v>
-      </c>
-      <c r="K133" t="s">
-        <v>466</v>
-      </c>
-      <c r="O133" s="3" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="134" spans="9:15" x14ac:dyDescent="0.25">
@@ -6018,13 +6013,13 @@
         <v>458</v>
       </c>
       <c r="J134" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="K134" t="s">
+        <v>467</v>
+      </c>
+      <c r="O134" s="3" t="s">
         <v>468</v>
-      </c>
-      <c r="K134" t="s">
-        <v>468</v>
-      </c>
-      <c r="O134" s="3" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="135" spans="9:15" x14ac:dyDescent="0.25">
@@ -6032,10 +6027,10 @@
         <v>462</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K135" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O135" s="3"/>
     </row>
@@ -6044,13 +6039,13 @@
         <v>466</v>
       </c>
       <c r="J136" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="K136" t="s">
+        <v>470</v>
+      </c>
+      <c r="O136" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="K136" t="s">
-        <v>471</v>
-      </c>
-      <c r="O136" s="3" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="137" spans="9:15" x14ac:dyDescent="0.25">
@@ -6058,13 +6053,13 @@
         <v>470</v>
       </c>
       <c r="J137" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="K137" t="s">
+        <v>472</v>
+      </c>
+      <c r="O137" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="K137" t="s">
-        <v>473</v>
-      </c>
-      <c r="O137" s="3" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="138" spans="9:15" x14ac:dyDescent="0.25">
@@ -6072,13 +6067,13 @@
         <v>474</v>
       </c>
       <c r="J138" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="K138" t="s">
+        <v>474</v>
+      </c>
+      <c r="O138" s="3" t="s">
         <v>475</v>
-      </c>
-      <c r="K138" t="s">
-        <v>475</v>
-      </c>
-      <c r="O138" s="3" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="139" spans="9:15" x14ac:dyDescent="0.25">
@@ -6086,10 +6081,10 @@
         <v>478</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K139" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="O139" s="3"/>
     </row>
@@ -6098,13 +6093,13 @@
         <v>480</v>
       </c>
       <c r="J140" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="K140" t="s">
+        <v>477</v>
+      </c>
+      <c r="O140" s="3" t="s">
         <v>478</v>
-      </c>
-      <c r="K140" t="s">
-        <v>478</v>
-      </c>
-      <c r="O140" s="3" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="141" spans="9:15" x14ac:dyDescent="0.25">
@@ -6112,13 +6107,13 @@
         <v>484</v>
       </c>
       <c r="J141" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K141" t="s">
+        <v>479</v>
+      </c>
+      <c r="O141" s="3" t="s">
         <v>480</v>
-      </c>
-      <c r="K141" t="s">
-        <v>480</v>
-      </c>
-      <c r="O141" s="3" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="142" spans="9:15" x14ac:dyDescent="0.25">
@@ -6126,13 +6121,13 @@
         <v>492</v>
       </c>
       <c r="J142" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="K142" t="s">
+        <v>481</v>
+      </c>
+      <c r="O142" s="3" t="s">
         <v>482</v>
-      </c>
-      <c r="K142" t="s">
-        <v>482</v>
-      </c>
-      <c r="O142" s="3" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="143" spans="9:15" x14ac:dyDescent="0.25">
@@ -6140,13 +6135,13 @@
         <v>496</v>
       </c>
       <c r="J143" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="K143" t="s">
+        <v>483</v>
+      </c>
+      <c r="O143" s="3" t="s">
         <v>484</v>
-      </c>
-      <c r="K143" t="s">
-        <v>484</v>
-      </c>
-      <c r="O143" s="3" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="144" spans="9:15" x14ac:dyDescent="0.25">
@@ -6154,10 +6149,10 @@
         <v>498</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K144" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="O144" s="3"/>
     </row>
@@ -6166,13 +6161,13 @@
         <v>499</v>
       </c>
       <c r="J145" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="K145" t="s">
+        <v>486</v>
+      </c>
+      <c r="O145" s="3" t="s">
         <v>487</v>
-      </c>
-      <c r="K145" t="s">
-        <v>487</v>
-      </c>
-      <c r="O145" s="3" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="146" spans="9:15" x14ac:dyDescent="0.25">
@@ -6180,10 +6175,10 @@
         <v>500</v>
       </c>
       <c r="J146" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="K146" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O146" s="3"/>
     </row>
@@ -6192,10 +6187,10 @@
         <v>504</v>
       </c>
       <c r="J147" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K147" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="O147" s="3"/>
     </row>
@@ -6204,13 +6199,13 @@
         <v>508</v>
       </c>
       <c r="J148" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="K148" t="s">
+        <v>490</v>
+      </c>
+      <c r="O148" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="K148" t="s">
-        <v>491</v>
-      </c>
-      <c r="O148" s="3" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="149" spans="9:15" x14ac:dyDescent="0.25">
@@ -6218,13 +6213,13 @@
         <v>512</v>
       </c>
       <c r="J149" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="K149" t="s">
+        <v>492</v>
+      </c>
+      <c r="O149" s="3" t="s">
         <v>493</v>
-      </c>
-      <c r="K149" t="s">
-        <v>493</v>
-      </c>
-      <c r="O149" s="3" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="150" spans="9:15" x14ac:dyDescent="0.25">
@@ -6232,13 +6227,13 @@
         <v>516</v>
       </c>
       <c r="J150" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="K150" t="s">
+        <v>494</v>
+      </c>
+      <c r="O150" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="K150" t="s">
-        <v>495</v>
-      </c>
-      <c r="O150" s="3" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="151" spans="9:15" x14ac:dyDescent="0.25">
@@ -6246,13 +6241,13 @@
         <v>520</v>
       </c>
       <c r="J151" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="K151" t="s">
+        <v>496</v>
+      </c>
+      <c r="O151" s="3" t="s">
         <v>497</v>
-      </c>
-      <c r="K151" t="s">
-        <v>497</v>
-      </c>
-      <c r="O151" s="3" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="152" spans="9:15" x14ac:dyDescent="0.25">
@@ -6260,13 +6255,13 @@
         <v>524</v>
       </c>
       <c r="J152" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="K152" t="s">
+        <v>498</v>
+      </c>
+      <c r="O152" s="3" t="s">
         <v>499</v>
-      </c>
-      <c r="K152" t="s">
-        <v>499</v>
-      </c>
-      <c r="O152" s="3" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="153" spans="9:15" x14ac:dyDescent="0.25">
@@ -6274,10 +6269,10 @@
         <v>528</v>
       </c>
       <c r="J153" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K153" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="O153" s="3"/>
     </row>
@@ -6286,13 +6281,13 @@
         <v>531</v>
       </c>
       <c r="J154" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="K154" t="s">
+        <v>501</v>
+      </c>
+      <c r="O154" s="3" t="s">
         <v>502</v>
-      </c>
-      <c r="K154" t="s">
-        <v>502</v>
-      </c>
-      <c r="O154" s="3" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="155" spans="9:15" x14ac:dyDescent="0.25">
@@ -6300,10 +6295,10 @@
         <v>533</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K155" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="O155" s="3"/>
     </row>
@@ -6312,10 +6307,10 @@
         <v>534</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K156" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O156" s="3"/>
     </row>
@@ -6324,10 +6319,10 @@
         <v>535</v>
       </c>
       <c r="J157" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K157" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="O157" s="3"/>
     </row>
@@ -6336,10 +6331,10 @@
         <v>540</v>
       </c>
       <c r="J158" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K158" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="O158" s="3"/>
     </row>
@@ -6348,10 +6343,10 @@
         <v>548</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K159" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="O159" s="3"/>
     </row>
@@ -6360,13 +6355,13 @@
         <v>554</v>
       </c>
       <c r="J160" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="K160" t="s">
+        <v>508</v>
+      </c>
+      <c r="O160" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="K160" t="s">
-        <v>509</v>
-      </c>
-      <c r="O160" s="3" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="161" spans="9:15" x14ac:dyDescent="0.25">
@@ -6374,10 +6369,10 @@
         <v>558</v>
       </c>
       <c r="J161" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K161" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O161" s="3"/>
     </row>
@@ -6386,13 +6381,13 @@
         <v>562</v>
       </c>
       <c r="J162" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="K162" t="s">
+        <v>511</v>
+      </c>
+      <c r="O162" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="K162" t="s">
-        <v>512</v>
-      </c>
-      <c r="O162" s="3" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="163" spans="9:15" x14ac:dyDescent="0.25">
@@ -6400,13 +6395,13 @@
         <v>566</v>
       </c>
       <c r="J163" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="K163" t="s">
+        <v>513</v>
+      </c>
+      <c r="O163" s="3" t="s">
         <v>514</v>
-      </c>
-      <c r="K163" t="s">
-        <v>514</v>
-      </c>
-      <c r="O163" s="3" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="164" spans="9:15" x14ac:dyDescent="0.25">
@@ -6414,13 +6409,13 @@
         <v>570</v>
       </c>
       <c r="J164" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="K164" t="s">
+        <v>515</v>
+      </c>
+      <c r="O164" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="K164" t="s">
-        <v>516</v>
-      </c>
-      <c r="O164" s="3" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="165" spans="9:15" x14ac:dyDescent="0.25">
@@ -6428,13 +6423,13 @@
         <v>574</v>
       </c>
       <c r="J165" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="K165" t="s">
+        <v>517</v>
+      </c>
+      <c r="O165" s="3" t="s">
         <v>518</v>
-      </c>
-      <c r="K165" t="s">
-        <v>518</v>
-      </c>
-      <c r="O165" s="3" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="166" spans="9:15" x14ac:dyDescent="0.25">
@@ -6442,10 +6437,10 @@
         <v>578</v>
       </c>
       <c r="J166" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K166" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="O166" s="3"/>
     </row>
@@ -6454,13 +6449,13 @@
         <v>580</v>
       </c>
       <c r="J167" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="K167" t="s">
+        <v>520</v>
+      </c>
+      <c r="O167" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="K167" t="s">
-        <v>521</v>
-      </c>
-      <c r="O167" s="3" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="168" spans="9:15" x14ac:dyDescent="0.25">
@@ -6468,13 +6463,13 @@
         <v>581</v>
       </c>
       <c r="J168" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="K168" t="s">
+        <v>522</v>
+      </c>
+      <c r="O168" s="3" t="s">
         <v>523</v>
-      </c>
-      <c r="K168" t="s">
-        <v>523</v>
-      </c>
-      <c r="O168" s="3" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="169" spans="9:15" x14ac:dyDescent="0.25">
@@ -6482,10 +6477,10 @@
         <v>583</v>
       </c>
       <c r="J169" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K169" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="O169" s="3"/>
     </row>
@@ -6494,13 +6489,13 @@
         <v>584</v>
       </c>
       <c r="J170" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="K170" t="s">
+        <v>525</v>
+      </c>
+      <c r="O170" s="3" t="s">
         <v>526</v>
-      </c>
-      <c r="K170" t="s">
-        <v>526</v>
-      </c>
-      <c r="O170" s="3" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="171" spans="9:15" x14ac:dyDescent="0.25">
@@ -6508,13 +6503,13 @@
         <v>585</v>
       </c>
       <c r="J171" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="K171" t="s">
+        <v>527</v>
+      </c>
+      <c r="O171" s="3" t="s">
         <v>528</v>
-      </c>
-      <c r="K171" t="s">
-        <v>528</v>
-      </c>
-      <c r="O171" s="3" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="172" spans="9:15" x14ac:dyDescent="0.25">
@@ -6522,13 +6517,13 @@
         <v>586</v>
       </c>
       <c r="J172" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="K172" t="s">
+        <v>529</v>
+      </c>
+      <c r="O172" s="3" t="s">
         <v>530</v>
-      </c>
-      <c r="K172" t="s">
-        <v>530</v>
-      </c>
-      <c r="O172" s="3" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="173" spans="9:15" x14ac:dyDescent="0.25">
@@ -6536,13 +6531,13 @@
         <v>591</v>
       </c>
       <c r="J173" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="K173" t="s">
+        <v>531</v>
+      </c>
+      <c r="O173" s="3" t="s">
         <v>532</v>
-      </c>
-      <c r="K173" t="s">
-        <v>532</v>
-      </c>
-      <c r="O173" s="3" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="174" spans="9:15" x14ac:dyDescent="0.25">
@@ -6550,13 +6545,13 @@
         <v>598</v>
       </c>
       <c r="J174" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="K174" t="s">
+        <v>533</v>
+      </c>
+      <c r="O174" s="3" t="s">
         <v>534</v>
-      </c>
-      <c r="K174" t="s">
-        <v>534</v>
-      </c>
-      <c r="O174" s="3" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="175" spans="9:15" x14ac:dyDescent="0.25">
@@ -6564,13 +6559,13 @@
         <v>600</v>
       </c>
       <c r="J175" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="K175" t="s">
+        <v>535</v>
+      </c>
+      <c r="O175" s="3" t="s">
         <v>536</v>
-      </c>
-      <c r="K175" t="s">
-        <v>536</v>
-      </c>
-      <c r="O175" s="3" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="176" spans="9:15" x14ac:dyDescent="0.25">
@@ -6578,13 +6573,13 @@
         <v>604</v>
       </c>
       <c r="J176" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="K176" t="s">
+        <v>537</v>
+      </c>
+      <c r="O176" s="3" t="s">
         <v>538</v>
-      </c>
-      <c r="K176" t="s">
-        <v>538</v>
-      </c>
-      <c r="O176" s="3" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="177" spans="9:15" x14ac:dyDescent="0.25">
@@ -6592,13 +6587,13 @@
         <v>608</v>
       </c>
       <c r="J177" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="K177" t="s">
+        <v>539</v>
+      </c>
+      <c r="O177" s="3" t="s">
         <v>540</v>
-      </c>
-      <c r="K177" t="s">
-        <v>540</v>
-      </c>
-      <c r="O177" s="3" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="178" spans="9:15" x14ac:dyDescent="0.25">
@@ -6606,13 +6601,13 @@
         <v>612</v>
       </c>
       <c r="J178" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="K178" t="s">
+        <v>541</v>
+      </c>
+      <c r="O178" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="K178" t="s">
-        <v>542</v>
-      </c>
-      <c r="O178" s="3" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="179" spans="9:15" x14ac:dyDescent="0.25">
@@ -6620,10 +6615,10 @@
         <v>616</v>
       </c>
       <c r="J179" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K179" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="O179" s="3"/>
     </row>
@@ -6632,13 +6627,13 @@
         <v>620</v>
       </c>
       <c r="J180" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="K180" t="s">
+        <v>544</v>
+      </c>
+      <c r="O180" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="K180" t="s">
-        <v>545</v>
-      </c>
-      <c r="O180" s="3" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="181" spans="9:15" x14ac:dyDescent="0.25">
@@ -6646,13 +6641,13 @@
         <v>624</v>
       </c>
       <c r="J181" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="K181" t="s">
+        <v>546</v>
+      </c>
+      <c r="O181" s="3" t="s">
         <v>547</v>
-      </c>
-      <c r="K181" t="s">
-        <v>547</v>
-      </c>
-      <c r="O181" s="3" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="182" spans="9:15" x14ac:dyDescent="0.25">
@@ -6660,13 +6655,13 @@
         <v>626</v>
       </c>
       <c r="J182" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="K182" t="s">
+        <v>548</v>
+      </c>
+      <c r="O182" s="3" t="s">
         <v>549</v>
-      </c>
-      <c r="K182" t="s">
-        <v>549</v>
-      </c>
-      <c r="O182" s="3" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="183" spans="9:15" x14ac:dyDescent="0.25">
@@ -6674,13 +6669,13 @@
         <v>630</v>
       </c>
       <c r="J183" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="K183" t="s">
+        <v>550</v>
+      </c>
+      <c r="O183" s="3" t="s">
         <v>551</v>
-      </c>
-      <c r="K183" t="s">
-        <v>551</v>
-      </c>
-      <c r="O183" s="3" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="184" spans="9:15" x14ac:dyDescent="0.25">
@@ -6688,10 +6683,10 @@
         <v>634</v>
       </c>
       <c r="J184" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K184" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="O184" s="3"/>
     </row>
@@ -6700,13 +6695,13 @@
         <v>638</v>
       </c>
       <c r="J185" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="K185" t="s">
+        <v>553</v>
+      </c>
+      <c r="O185" s="3" t="s">
         <v>554</v>
-      </c>
-      <c r="K185" t="s">
-        <v>554</v>
-      </c>
-      <c r="O185" s="3" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="186" spans="9:15" x14ac:dyDescent="0.25">
@@ -6714,10 +6709,10 @@
         <v>642</v>
       </c>
       <c r="J186" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K186" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="O186" s="3"/>
     </row>
@@ -6738,13 +6733,13 @@
         <v>646</v>
       </c>
       <c r="J188" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="K188" t="s">
+        <v>556</v>
+      </c>
+      <c r="O188" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="K188" t="s">
-        <v>557</v>
-      </c>
-      <c r="O188" s="3" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="189" spans="9:15" x14ac:dyDescent="0.25">
@@ -6752,13 +6747,13 @@
         <v>652</v>
       </c>
       <c r="J189" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="K189" t="s">
+        <v>558</v>
+      </c>
+      <c r="O189" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="K189" t="s">
-        <v>559</v>
-      </c>
-      <c r="O189" s="3" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="190" spans="9:15" x14ac:dyDescent="0.25">
@@ -6766,10 +6761,10 @@
         <v>654</v>
       </c>
       <c r="J190" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K190" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="O190" s="3"/>
     </row>
@@ -6778,10 +6773,10 @@
         <v>659</v>
       </c>
       <c r="J191" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K191" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="O191" s="3"/>
     </row>
@@ -6790,10 +6785,10 @@
         <v>660</v>
       </c>
       <c r="J192" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="K192" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="O192" s="3"/>
     </row>
@@ -6802,10 +6797,10 @@
         <v>662</v>
       </c>
       <c r="J193" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K193" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="O193" s="3"/>
     </row>
@@ -6814,10 +6809,10 @@
         <v>663</v>
       </c>
       <c r="J194" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="K194" t="s">
         <v>565</v>
-      </c>
-      <c r="K194" t="s">
-        <v>566</v>
       </c>
       <c r="O194" s="3"/>
     </row>
@@ -6826,10 +6821,10 @@
         <v>666</v>
       </c>
       <c r="J195" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="K195" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="O195" s="3"/>
     </row>
@@ -6838,10 +6833,10 @@
         <v>670</v>
       </c>
       <c r="J196" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K196" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="O196" s="3"/>
     </row>
@@ -6850,10 +6845,10 @@
         <v>674</v>
       </c>
       <c r="J197" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K197" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="O197" s="3"/>
     </row>
@@ -6862,13 +6857,13 @@
         <v>678</v>
       </c>
       <c r="J198" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="K198" t="s">
+        <v>569</v>
+      </c>
+      <c r="O198" s="3" t="s">
         <v>570</v>
-      </c>
-      <c r="K198" t="s">
-        <v>570</v>
-      </c>
-      <c r="O198" s="3" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="199" spans="9:15" x14ac:dyDescent="0.25">
@@ -6876,13 +6871,13 @@
         <v>682</v>
       </c>
       <c r="J199" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="K199" t="s">
+        <v>571</v>
+      </c>
+      <c r="O199" s="3" t="s">
         <v>572</v>
-      </c>
-      <c r="K199" t="s">
-        <v>572</v>
-      </c>
-      <c r="O199" s="3" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="200" spans="9:15" x14ac:dyDescent="0.25">
@@ -6890,13 +6885,13 @@
         <v>686</v>
       </c>
       <c r="J200" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="K200" t="s">
+        <v>573</v>
+      </c>
+      <c r="O200" s="3" t="s">
         <v>574</v>
-      </c>
-      <c r="K200" t="s">
-        <v>574</v>
-      </c>
-      <c r="O200" s="3" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="201" spans="9:15" x14ac:dyDescent="0.25">
@@ -6904,13 +6899,13 @@
         <v>688</v>
       </c>
       <c r="J201" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="K201" t="s">
+        <v>575</v>
+      </c>
+      <c r="O201" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="K201" t="s">
-        <v>576</v>
-      </c>
-      <c r="O201" s="3" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="202" spans="9:15" x14ac:dyDescent="0.25">
@@ -6918,13 +6913,13 @@
         <v>690</v>
       </c>
       <c r="J202" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="K202" t="s">
+        <v>577</v>
+      </c>
+      <c r="O202" s="3" t="s">
         <v>578</v>
-      </c>
-      <c r="K202" t="s">
-        <v>578</v>
-      </c>
-      <c r="O202" s="3" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="203" spans="9:15" x14ac:dyDescent="0.25">
@@ -6932,13 +6927,13 @@
         <v>694</v>
       </c>
       <c r="J203" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="K203" t="s">
+        <v>579</v>
+      </c>
+      <c r="O203" s="3" t="s">
         <v>580</v>
-      </c>
-      <c r="K203" t="s">
-        <v>580</v>
-      </c>
-      <c r="O203" s="3" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="204" spans="9:15" x14ac:dyDescent="0.25">
@@ -6946,13 +6941,13 @@
         <v>702</v>
       </c>
       <c r="J204" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="K204" t="s">
+        <v>581</v>
+      </c>
+      <c r="O204" s="3" t="s">
         <v>582</v>
-      </c>
-      <c r="K204" t="s">
-        <v>582</v>
-      </c>
-      <c r="O204" s="3" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="205" spans="9:15" x14ac:dyDescent="0.25">
@@ -6960,13 +6955,13 @@
         <v>703</v>
       </c>
       <c r="J205" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="K205" t="s">
+        <v>583</v>
+      </c>
+      <c r="O205" s="3" t="s">
         <v>584</v>
-      </c>
-      <c r="K205" t="s">
-        <v>584</v>
-      </c>
-      <c r="O205" s="3" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="206" spans="9:15" x14ac:dyDescent="0.25">
@@ -6974,13 +6969,13 @@
         <v>704</v>
       </c>
       <c r="J206" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="K206" t="s">
+        <v>585</v>
+      </c>
+      <c r="O206" s="3" t="s">
         <v>586</v>
-      </c>
-      <c r="K206" t="s">
-        <v>586</v>
-      </c>
-      <c r="O206" s="3" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="207" spans="9:15" x14ac:dyDescent="0.25">
@@ -6988,13 +6983,13 @@
         <v>705</v>
       </c>
       <c r="J207" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="K207" t="s">
+        <v>587</v>
+      </c>
+      <c r="O207" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="K207" t="s">
-        <v>588</v>
-      </c>
-      <c r="O207" s="3" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="208" spans="9:15" x14ac:dyDescent="0.25">
@@ -7002,13 +6997,13 @@
         <v>706</v>
       </c>
       <c r="J208" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="K208" t="s">
+        <v>589</v>
+      </c>
+      <c r="O208" s="3" t="s">
         <v>590</v>
-      </c>
-      <c r="K208" t="s">
-        <v>590</v>
-      </c>
-      <c r="O208" s="3" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="209" spans="9:15" x14ac:dyDescent="0.25">
@@ -7016,13 +7011,13 @@
         <v>710</v>
       </c>
       <c r="J209" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="K209" t="s">
+        <v>591</v>
+      </c>
+      <c r="O209" s="3" t="s">
         <v>592</v>
-      </c>
-      <c r="K209" t="s">
-        <v>592</v>
-      </c>
-      <c r="O209" s="3" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="210" spans="9:15" x14ac:dyDescent="0.25">
@@ -7030,13 +7025,13 @@
         <v>716</v>
       </c>
       <c r="J210" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="K210" t="s">
+        <v>593</v>
+      </c>
+      <c r="O210" s="3" t="s">
         <v>594</v>
-      </c>
-      <c r="K210" t="s">
-        <v>594</v>
-      </c>
-      <c r="O210" s="3" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="211" spans="9:15" x14ac:dyDescent="0.25">
@@ -7044,13 +7039,13 @@
         <v>724</v>
       </c>
       <c r="J211" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="K211" t="s">
+        <v>595</v>
+      </c>
+      <c r="O211" s="3" t="s">
         <v>596</v>
-      </c>
-      <c r="K211" t="s">
-        <v>596</v>
-      </c>
-      <c r="O211" s="3" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="212" spans="9:15" x14ac:dyDescent="0.25">
@@ -7058,13 +7053,13 @@
         <v>732</v>
       </c>
       <c r="J212" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="K212" t="s">
         <v>598</v>
       </c>
-      <c r="K212" t="s">
+      <c r="O212" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="O212" s="3" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="213" spans="9:15" x14ac:dyDescent="0.25">
@@ -7072,10 +7067,10 @@
         <v>729</v>
       </c>
       <c r="J213" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="K213" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O213" s="3"/>
     </row>
@@ -7084,13 +7079,13 @@
         <v>740</v>
       </c>
       <c r="J214" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="K214" t="s">
+        <v>597</v>
+      </c>
+      <c r="O214" s="3" t="s">
         <v>602</v>
-      </c>
-      <c r="K214" t="s">
-        <v>598</v>
-      </c>
-      <c r="O214" s="3" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="215" spans="9:15" x14ac:dyDescent="0.25">
@@ -7098,13 +7093,13 @@
         <v>744</v>
       </c>
       <c r="J215" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="K215" t="s">
+        <v>601</v>
+      </c>
+      <c r="O215" s="3" t="s">
         <v>604</v>
-      </c>
-      <c r="K215" t="s">
-        <v>602</v>
-      </c>
-      <c r="O215" s="3" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="216" spans="9:15" x14ac:dyDescent="0.25">
@@ -7112,10 +7107,10 @@
         <v>748</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K216" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="O216" s="3"/>
     </row>
@@ -7124,13 +7119,13 @@
         <v>752</v>
       </c>
       <c r="J217" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="K217" t="s">
+        <v>605</v>
+      </c>
+      <c r="O217" s="3" t="s">
         <v>607</v>
-      </c>
-      <c r="K217" t="s">
-        <v>606</v>
-      </c>
-      <c r="O217" s="3" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="218" spans="9:15" x14ac:dyDescent="0.25">
@@ -7138,13 +7133,13 @@
         <v>756</v>
       </c>
       <c r="J218" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="K218" t="s">
+        <v>606</v>
+      </c>
+      <c r="O218" s="3" t="s">
         <v>609</v>
-      </c>
-      <c r="K218" t="s">
-        <v>607</v>
-      </c>
-      <c r="O218" s="3" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="219" spans="9:15" x14ac:dyDescent="0.25">
@@ -7152,13 +7147,13 @@
         <v>760</v>
       </c>
       <c r="J219" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="K219" t="s">
+        <v>608</v>
+      </c>
+      <c r="O219" s="3" t="s">
         <v>611</v>
-      </c>
-      <c r="K219" t="s">
-        <v>609</v>
-      </c>
-      <c r="O219" s="3" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="220" spans="9:15" x14ac:dyDescent="0.25">
@@ -7166,10 +7161,10 @@
         <v>762</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K220" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O220" s="3"/>
     </row>
@@ -7178,13 +7173,13 @@
         <v>764</v>
       </c>
       <c r="J221" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="K221" t="s">
+        <v>612</v>
+      </c>
+      <c r="O221" s="3" t="s">
         <v>614</v>
-      </c>
-      <c r="K221" t="s">
-        <v>613</v>
-      </c>
-      <c r="O221" s="3" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="222" spans="9:15" x14ac:dyDescent="0.25">
@@ -7192,13 +7187,13 @@
         <v>768</v>
       </c>
       <c r="J222" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="K222" t="s">
+        <v>613</v>
+      </c>
+      <c r="O222" s="3" t="s">
         <v>616</v>
-      </c>
-      <c r="K222" t="s">
-        <v>614</v>
-      </c>
-      <c r="O222" s="3" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="223" spans="9:15" x14ac:dyDescent="0.25">
@@ -7206,13 +7201,13 @@
         <v>772</v>
       </c>
       <c r="J223" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="K223" t="s">
+        <v>615</v>
+      </c>
+      <c r="O223" s="3" t="s">
         <v>618</v>
-      </c>
-      <c r="K223" t="s">
-        <v>616</v>
-      </c>
-      <c r="O223" s="3" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="224" spans="9:15" x14ac:dyDescent="0.25">
@@ -7220,10 +7215,10 @@
         <v>776</v>
       </c>
       <c r="J224" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K224" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="O224" s="3"/>
     </row>
@@ -7232,13 +7227,13 @@
         <v>780</v>
       </c>
       <c r="J225" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="K225" t="s">
+        <v>619</v>
+      </c>
+      <c r="O225" s="3" t="s">
         <v>621</v>
-      </c>
-      <c r="K225" t="s">
-        <v>620</v>
-      </c>
-      <c r="O225" s="3" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="226" spans="9:15" x14ac:dyDescent="0.25">
@@ -7246,13 +7241,13 @@
         <v>784</v>
       </c>
       <c r="J226" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="K226" t="s">
+        <v>620</v>
+      </c>
+      <c r="O226" s="3" t="s">
         <v>623</v>
-      </c>
-      <c r="K226" t="s">
-        <v>621</v>
-      </c>
-      <c r="O226" s="3" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="227" spans="9:15" x14ac:dyDescent="0.25">
@@ -7260,10 +7255,10 @@
         <v>788</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K227" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="O227" s="3"/>
     </row>
@@ -7272,13 +7267,13 @@
         <v>792</v>
       </c>
       <c r="J228" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="K228" t="s">
+        <v>624</v>
+      </c>
+      <c r="O228" s="3" t="s">
         <v>626</v>
-      </c>
-      <c r="K228" t="s">
-        <v>625</v>
-      </c>
-      <c r="O228" s="3" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="229" spans="9:15" x14ac:dyDescent="0.25">
@@ -7286,13 +7281,13 @@
         <v>795</v>
       </c>
       <c r="J229" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="K229" t="s">
+        <v>625</v>
+      </c>
+      <c r="O229" s="3" t="s">
         <v>628</v>
-      </c>
-      <c r="K229" t="s">
-        <v>626</v>
-      </c>
-      <c r="O229" s="3" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="230" spans="9:15" x14ac:dyDescent="0.25">
@@ -7300,13 +7295,13 @@
         <v>796</v>
       </c>
       <c r="J230" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="K230" t="s">
+        <v>627</v>
+      </c>
+      <c r="O230" s="3" t="s">
         <v>630</v>
-      </c>
-      <c r="K230" t="s">
-        <v>628</v>
-      </c>
-      <c r="O230" s="3" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="231" spans="9:15" x14ac:dyDescent="0.25">
@@ -7314,10 +7309,10 @@
         <v>798</v>
       </c>
       <c r="J231" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K231" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="O231" s="3"/>
     </row>
@@ -7326,10 +7321,10 @@
         <v>800</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="K232" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="O232" s="3"/>
     </row>
@@ -7338,13 +7333,13 @@
         <v>804</v>
       </c>
       <c r="J233" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="K233" t="s">
+        <v>632</v>
+      </c>
+      <c r="O233" s="3" t="s">
         <v>634</v>
-      </c>
-      <c r="K233" t="s">
-        <v>633</v>
-      </c>
-      <c r="O233" s="3" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="234" spans="9:15" x14ac:dyDescent="0.25">
@@ -7352,10 +7347,10 @@
         <v>807</v>
       </c>
       <c r="J234" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="K234" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="O234" s="3"/>
     </row>
@@ -7364,13 +7359,13 @@
         <v>818</v>
       </c>
       <c r="J235" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="K235" t="s">
+        <v>635</v>
+      </c>
+      <c r="O235" s="3" t="s">
         <v>637</v>
-      </c>
-      <c r="K235" t="s">
-        <v>636</v>
-      </c>
-      <c r="O235" s="3" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="236" spans="9:15" x14ac:dyDescent="0.25">
@@ -7378,13 +7373,13 @@
         <v>826</v>
       </c>
       <c r="J236" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="K236" t="s">
+        <v>636</v>
+      </c>
+      <c r="O236" s="3" t="s">
         <v>639</v>
-      </c>
-      <c r="K236" t="s">
-        <v>637</v>
-      </c>
-      <c r="O236" s="3" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="237" spans="9:15" x14ac:dyDescent="0.25">
@@ -7392,13 +7387,13 @@
         <v>831</v>
       </c>
       <c r="J237" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="K237" t="s">
+        <v>638</v>
+      </c>
+      <c r="O237" s="3" t="s">
         <v>641</v>
-      </c>
-      <c r="K237" t="s">
-        <v>639</v>
-      </c>
-      <c r="O237" s="3" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="238" spans="9:15" x14ac:dyDescent="0.25">
@@ -7406,10 +7401,10 @@
         <v>832</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="K238" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="O238" s="3"/>
     </row>
@@ -7418,10 +7413,10 @@
         <v>833</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="K239" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="O239" s="3"/>
     </row>
@@ -7430,10 +7425,10 @@
         <v>834</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="K240" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="O240" s="3"/>
     </row>
@@ -7442,13 +7437,13 @@
         <v>840</v>
       </c>
       <c r="J241" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="K241" t="s">
+        <v>644</v>
+      </c>
+      <c r="O241" s="3" t="s">
         <v>646</v>
-      </c>
-      <c r="K241" t="s">
-        <v>645</v>
-      </c>
-      <c r="O241" s="3" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="242" spans="9:15" x14ac:dyDescent="0.25">
@@ -7456,13 +7451,13 @@
         <v>850</v>
       </c>
       <c r="J242" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="K242" t="s">
+        <v>645</v>
+      </c>
+      <c r="O242" s="3" t="s">
         <v>648</v>
-      </c>
-      <c r="K242" t="s">
-        <v>646</v>
-      </c>
-      <c r="O242" s="3" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="243" spans="9:15" x14ac:dyDescent="0.25">
@@ -7470,13 +7465,13 @@
         <v>854</v>
       </c>
       <c r="J243" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="K243" t="s">
+        <v>647</v>
+      </c>
+      <c r="O243" s="3" t="s">
         <v>650</v>
-      </c>
-      <c r="K243" t="s">
-        <v>648</v>
-      </c>
-      <c r="O243" s="3" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="244" spans="9:15" x14ac:dyDescent="0.25">
@@ -7484,10 +7479,10 @@
         <v>858</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="K244" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="O244" s="3"/>
     </row>
@@ -7496,13 +7491,13 @@
         <v>860</v>
       </c>
       <c r="J245" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="K245" t="s">
+        <v>651</v>
+      </c>
+      <c r="O245" s="3" t="s">
         <v>653</v>
-      </c>
-      <c r="K245" t="s">
-        <v>652</v>
-      </c>
-      <c r="O245" s="3" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="246" spans="9:15" x14ac:dyDescent="0.25">
@@ -7510,13 +7505,13 @@
         <v>862</v>
       </c>
       <c r="J246" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="K246" t="s">
+        <v>652</v>
+      </c>
+      <c r="O246" s="3" t="s">
         <v>655</v>
-      </c>
-      <c r="K246" t="s">
-        <v>653</v>
-      </c>
-      <c r="O246" s="3" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="247" spans="9:15" x14ac:dyDescent="0.25">
@@ -7524,13 +7519,13 @@
         <v>876</v>
       </c>
       <c r="J247" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="K247" t="s">
+        <v>654</v>
+      </c>
+      <c r="O247" s="3" t="s">
         <v>657</v>
-      </c>
-      <c r="K247" t="s">
-        <v>655</v>
-      </c>
-      <c r="O247" s="3" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="248" spans="9:15" x14ac:dyDescent="0.25">
@@ -7538,10 +7533,10 @@
         <v>882</v>
       </c>
       <c r="J248" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K248" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="O248" s="3"/>
     </row>
@@ -7550,13 +7545,13 @@
         <v>887</v>
       </c>
       <c r="J249" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="K249" t="s">
+        <v>658</v>
+      </c>
+      <c r="O249" s="3" t="s">
         <v>660</v>
-      </c>
-      <c r="K249" t="s">
-        <v>659</v>
-      </c>
-      <c r="O249" s="3" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="250" spans="9:15" x14ac:dyDescent="0.25">
@@ -7564,13 +7559,13 @@
         <v>894</v>
       </c>
       <c r="J250" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="K250" t="s">
+        <v>659</v>
+      </c>
+      <c r="O250" s="3" t="s">
         <v>662</v>
-      </c>
-      <c r="K250" t="s">
-        <v>660</v>
-      </c>
-      <c r="O250" s="3" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="251" spans="9:15" x14ac:dyDescent="0.25">
@@ -7578,13 +7573,13 @@
         <v>895</v>
       </c>
       <c r="J251" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="K251" t="s">
+        <v>661</v>
+      </c>
+      <c r="O251" s="3" t="s">
         <v>664</v>
-      </c>
-      <c r="K251" t="s">
-        <v>662</v>
-      </c>
-      <c r="O251" s="3" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="252" spans="9:15" x14ac:dyDescent="0.25">
@@ -7592,13 +7587,13 @@
         <v>896</v>
       </c>
       <c r="J252" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="K252" t="s">
+        <v>663</v>
+      </c>
+      <c r="O252" s="3" t="s">
         <v>666</v>
-      </c>
-      <c r="K252" t="s">
-        <v>664</v>
-      </c>
-      <c r="O252" s="3" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="253" spans="9:15" x14ac:dyDescent="0.25">
@@ -7606,18 +7601,18 @@
         <v>728</v>
       </c>
       <c r="J253" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="K253" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="O253" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="254" spans="9:15" x14ac:dyDescent="0.25">
       <c r="O254" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
   </sheetData>
